--- a/Analysis/RAG_Ablation/rag_ablation_friedman_tests.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_friedman_tests.xlsx
@@ -455,16 +455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.44769874476984</v>
+        <v>9.896382730455214</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08676438750970707</v>
+        <v>0.1945218115466549</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.5313565098842</v>
+        <v>79.96682590233554</v>
       </c>
       <c r="C3" t="n">
-        <v>3.719511924256735e-06</v>
+        <v>1.399126260251591e-14</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
@@ -499,16 +499,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.67427597955714</v>
+        <v>78.99628597957295</v>
       </c>
       <c r="C4" t="n">
-        <v>5.406236632854256e-06</v>
+        <v>2.206410209476672e-14</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.22666666666678</v>
+        <v>8.666666666666892</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09334691320701217</v>
+        <v>0.27748196606419</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="F5" t="n">
         <v>8</v>

--- a/Analysis/RAG_Ablation/rag_ablation_friedman_tests.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_friedman_tests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,16 @@
           <t>n_configs</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>p_holm</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>significant_holm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +479,12 @@
       <c r="F2" t="n">
         <v>8</v>
       </c>
+      <c r="G2" t="n">
+        <v>0.3890436230933099</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -477,10 +493,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.96682590233554</v>
+        <v>80.05175846051749</v>
       </c>
       <c r="C3" t="n">
-        <v>1.399126260251591e-14</v>
+        <v>1.344427728869383e-14</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -490,6 +506,12 @@
       </c>
       <c r="F3" t="n">
         <v>8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.377710915477533e-14</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -513,6 +535,12 @@
       <c r="F4" t="n">
         <v>8</v>
       </c>
+      <c r="G4" t="n">
+        <v>6.619230628430016e-14</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -534,6 +562,12 @@
       </c>
       <c r="F5" t="n">
         <v>8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.27748196606419</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/RAG_Ablation/rag_ablation_friedman_tests.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_friedman_tests.xlsx
@@ -413,46 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>model_key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>chi2</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>df</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>n_scenarios</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>n_configs</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>p_holm</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>significant_holm</t>
         </is>
@@ -461,112 +466,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>kendall_tau</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>9.896382730455214</v>
-      </c>
       <c r="C2" t="n">
-        <v>0.1945218115466549</v>
+        <v>43.32164767747577</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>1.007372374637591e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3890436230933099</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.051606622463138e-07</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>score_mae</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>80.05175846051749</v>
-      </c>
       <c r="C3" t="n">
-        <v>1.344427728869383e-14</v>
+        <v>62.09279806334511</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>1.689162287717664e-11</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="G3" t="n">
-        <v>5.377710915477533e-14</v>
-      </c>
-      <c r="H3" t="b">
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.520246058945898e-10</v>
+      </c>
+      <c r="I3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>score_rmse</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>78.99628597957295</v>
-      </c>
       <c r="C4" t="n">
-        <v>2.206410209476672e-14</v>
+        <v>67.9149193548388</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>1.093622966216266e-12</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>6.619230628430016e-14</v>
-      </c>
-      <c r="H4" t="b">
+        <v>7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.093622966216266e-11</v>
+      </c>
+      <c r="I4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>top1_accuracy</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>8.666666666666892</v>
-      </c>
       <c r="C5" t="n">
-        <v>0.27748196606419</v>
+        <v>20.93717277486957</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>0.001882911462851962</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
-        <v>0.27748196606419</v>
-      </c>
-      <c r="H5" t="b">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.00941455731425981</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>21.26658551430332</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0016428284712495</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.009856970827496998</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>155.3540728612365</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.702008384280726e-31</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>90</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9.123213414849161e-30</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>154.621323529412</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.148708976471782e-31</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>90</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.222306346470767e-29</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>43.72277227722795</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.389303769892583e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>90</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.711443015914067e-07</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15.38038632986625</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01749578482964076</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>89</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.06998313931856305</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>75.91944167497536</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.48193504513946e-14</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>90</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.978322054167352e-13</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>75.40824865511057</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.162868775058878e-14</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>90</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.479155652564767e-13</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8.104109589041574</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2305747947688351</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>90</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6917243843065054</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7.674958540630497</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2628967508400173</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>78</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5257935016800347</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>84.77222995822571</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.679987493672851e-16</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>90</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.783983741774706e-15</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>84.84386174016697</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.556379155737688e-16</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>90</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.978930818032763e-15</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6.772833723653753</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3423673685841852</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>90</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3423673685841852</v>
+      </c>
+      <c r="I17" t="b">
         <v>0</v>
       </c>
     </row>
